--- a/excel/Batch_09_Leads_Tracker.xlsx
+++ b/excel/Batch_09_Leads_Tracker.xlsx
@@ -530,10 +530,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L2" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N2" t="str">
         <v>Final check-in about your website</v>
@@ -611,10 +611,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L3" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N3" t="str">
         <v>Final check-in about your website</v>
@@ -692,10 +692,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L4" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N4" t="str">
         <v>Final check-in about your website</v>
@@ -733,8 +733,8 @@
         <v>07756 968944</v>
       </c>
       <c r="E5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facebook
-YouTube</v>
+        <v xml:space="preserve">Facebook: Facebook
+YouTube: YouTube</v>
       </c>
       <c r="F5" t="str">
         <v>A clearer website for Edmonton Green Painters &amp; Decorators</v>
@@ -774,10 +774,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L5" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N5" t="str">
         <v>Final check-in about your website</v>
@@ -855,10 +855,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L6" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N6" t="str">
         <v>Final check-in about your website</v>
@@ -936,10 +936,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L7" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N7" t="str">
         <v>Final check-in about your website</v>
@@ -1017,10 +1017,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L8" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N8" t="str">
         <v>Final check-in about your website</v>
@@ -1098,10 +1098,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L9" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N9" t="str">
         <v>Final check-in about your website</v>
@@ -1139,9 +1139,9 @@
         <v>07495 598189</v>
       </c>
       <c r="E10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facebook
-Instagram
-TikTok</v>
+        <v xml:space="preserve">Facebook: Facebook
+Instagram: Instagram
+TikTok: TikTok</v>
       </c>
       <c r="F10" t="str">
         <v>A clearer website for Kerry Plant Services</v>
@@ -1181,10 +1181,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L10" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N10" t="str">
         <v>Final check-in about your website</v>
@@ -1262,10 +1262,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L11" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N11" t="str">
         <v>Final check-in about your website</v>
@@ -1343,10 +1343,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L12" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N12" t="str">
         <v>Final check-in about your website</v>
@@ -1424,10 +1424,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L13" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N13" t="str">
         <v>Final check-in about your website</v>
@@ -1505,10 +1505,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L14" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N14" t="str">
         <v>Final check-in about your website</v>
@@ -1586,10 +1586,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L15" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N15" t="str">
         <v>Final check-in about your website</v>
@@ -1667,10 +1667,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L16" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N16" t="str">
         <v>Final check-in about your website</v>
@@ -1748,10 +1748,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L17" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N17" t="str">
         <v>Final check-in about your website</v>
@@ -1829,10 +1829,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L18" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N18" t="str">
         <v>Final check-in about your website</v>
@@ -1870,8 +1870,8 @@
         <v>020 8902 9298</v>
       </c>
       <c r="E19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Instagram
-LinkedIn</v>
+        <v xml:space="preserve">Instagram: Instagram
+LinkedIn: LinkedIn</v>
       </c>
       <c r="F19" t="str">
         <v>A clearer website for VC Print UK</v>
@@ -1911,10 +1911,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L19" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N19" t="str">
         <v>Final check-in about your website</v>
@@ -1992,10 +1992,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L20" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N20" t="str">
         <v>Final check-in about your website</v>
@@ -2033,10 +2033,10 @@
         <v>020 8629 1181</v>
       </c>
       <c r="E21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facebook
-Instagram
-YouTube
-Pinterest</v>
+        <v xml:space="preserve">Facebook: Facebook
+Instagram: Instagram
+YouTube: YouTube
+Pinterest: Pinterest</v>
       </c>
       <c r="F21" t="str">
         <v>A clearer website for Mecnitecs Mobile Mechanics</v>
@@ -2076,10 +2076,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L21" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N21" t="str">
         <v>Final check-in about your website</v>

--- a/excel/Batch_09_Leads_Tracker.xlsx
+++ b/excel/Batch_09_Leads_Tracker.xlsx
@@ -548,10 +548,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P2" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R2" t="str">
         <v/>
@@ -629,10 +629,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P3" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R3" t="str">
         <v/>
@@ -710,10 +710,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P4" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q4" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R4" t="str">
         <v/>
@@ -792,10 +792,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P5" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q5" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R5" t="str">
         <v/>
@@ -873,10 +873,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P6" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q6" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R6" t="str">
         <v/>
@@ -954,10 +954,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P7" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q7" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R7" t="str">
         <v/>
@@ -1035,10 +1035,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P8" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q8" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R8" t="str">
         <v/>
@@ -1116,10 +1116,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P9" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q9" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R9" t="str">
         <v/>
@@ -1199,10 +1199,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P10" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q10" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R10" t="str">
         <v/>
@@ -1280,10 +1280,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P11" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q11" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R11" t="str">
         <v/>
@@ -1361,10 +1361,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P12" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q12" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R12" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P13" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q13" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R13" t="str">
         <v/>
@@ -1523,10 +1523,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P14" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q14" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R14" t="str">
         <v/>
@@ -1604,10 +1604,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P15" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q15" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R15" t="str">
         <v/>
@@ -1685,10 +1685,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P16" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R16" t="str">
         <v/>
@@ -1766,10 +1766,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P17" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q17" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R17" t="str">
         <v/>
@@ -1847,10 +1847,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P18" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R18" t="str">
         <v/>
@@ -1929,10 +1929,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P19" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q19" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R19" t="str">
         <v/>
@@ -2010,10 +2010,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P20" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q20" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R20" t="str">
         <v/>
@@ -2094,10 +2094,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="P21" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="Q21" t="str">
-        <v/>
+        <v>2026-10-01</v>
       </c>
       <c r="R21" t="str">
         <v/>
